--- a/docs/tables/frame_count_study_summary.xlsx
+++ b/docs/tables/frame_count_study_summary.xlsx
@@ -516,7 +516,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>inlier RMSE@3cm (mm)</t>
+          <t>inlier RMSE@3cm (cm)</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -640,7 +640,7 @@
         <v>6.495</v>
       </c>
       <c r="J2" t="n">
-        <v>13.3</v>
+        <v>1.33</v>
       </c>
       <c r="K2" t="n">
         <v>88.47</v>
@@ -729,7 +729,7 @@
         <v>1.678</v>
       </c>
       <c r="J3" t="n">
-        <v>12.14</v>
+        <v>1.21</v>
       </c>
       <c r="K3" t="n">
         <v>91.39</v>
@@ -818,7 +818,7 @@
         <v>1.523</v>
       </c>
       <c r="J4" t="n">
-        <v>13.11</v>
+        <v>1.31</v>
       </c>
       <c r="K4" t="n">
         <v>89.8</v>
@@ -907,7 +907,7 @@
         <v>1.336</v>
       </c>
       <c r="J5" t="n">
-        <v>13.35</v>
+        <v>1.33</v>
       </c>
       <c r="K5" t="n">
         <v>92.95</v>
@@ -996,7 +996,7 @@
         <v>0.493</v>
       </c>
       <c r="J6" t="n">
-        <v>11.98</v>
+        <v>1.2</v>
       </c>
       <c r="K6" t="n">
         <v>90.42</v>
@@ -1085,7 +1085,7 @@
         <v>0.701</v>
       </c>
       <c r="J7" t="n">
-        <v>12.2</v>
+        <v>1.22</v>
       </c>
       <c r="K7" t="n">
         <v>90.75</v>
@@ -1174,7 +1174,7 @@
         <v>0.66</v>
       </c>
       <c r="J8" t="n">
-        <v>12.33</v>
+        <v>1.23</v>
       </c>
       <c r="K8" t="n">
         <v>90.84999999999999</v>
@@ -1263,7 +1263,7 @@
         <v>0.678</v>
       </c>
       <c r="J9" t="n">
-        <v>12.68</v>
+        <v>1.27</v>
       </c>
       <c r="K9" t="n">
         <v>90.62</v>
@@ -1352,7 +1352,7 @@
         <v>1.546</v>
       </c>
       <c r="J10" t="n">
-        <v>16.31</v>
+        <v>1.63</v>
       </c>
       <c r="K10" t="n">
         <v>74.14</v>
@@ -1441,7 +1441,7 @@
         <v>0.751</v>
       </c>
       <c r="J11" t="n">
-        <v>15</v>
+        <v>1.5</v>
       </c>
       <c r="K11" t="n">
         <v>80.08</v>
@@ -1530,7 +1530,7 @@
         <v>0.577</v>
       </c>
       <c r="J12" t="n">
-        <v>14.82</v>
+        <v>1.48</v>
       </c>
       <c r="K12" t="n">
         <v>81.51000000000001</v>
@@ -1619,7 +1619,7 @@
         <v>0.755</v>
       </c>
       <c r="J13" t="n">
-        <v>14.95</v>
+        <v>1.5</v>
       </c>
       <c r="K13" t="n">
         <v>82.53</v>
@@ -1708,7 +1708,7 @@
         <v>0.9360000000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>19.14</v>
+        <v>1.91</v>
       </c>
       <c r="K14" t="n">
         <v>74.37</v>
@@ -1797,7 +1797,7 @@
         <v>0.825</v>
       </c>
       <c r="J15" t="n">
-        <v>17.26</v>
+        <v>1.73</v>
       </c>
       <c r="K15" t="n">
         <v>72.98</v>
@@ -1886,7 +1886,7 @@
         <v>0.792</v>
       </c>
       <c r="J16" t="n">
-        <v>17.48</v>
+        <v>1.75</v>
       </c>
       <c r="K16" t="n">
         <v>75.54000000000001</v>
@@ -1975,7 +1975,7 @@
         <v>0.661</v>
       </c>
       <c r="J17" t="n">
-        <v>17.69</v>
+        <v>1.77</v>
       </c>
       <c r="K17" t="n">
         <v>72.62</v>
@@ -2064,7 +2064,7 @@
         <v>0.718</v>
       </c>
       <c r="J18" t="n">
-        <v>17.28</v>
+        <v>1.73</v>
       </c>
       <c r="K18" t="n">
         <v>75.23999999999999</v>
@@ -2153,7 +2153,7 @@
         <v>0.716</v>
       </c>
       <c r="J19" t="n">
-        <v>19.29</v>
+        <v>1.93</v>
       </c>
       <c r="K19" t="n">
         <v>73.36</v>
@@ -2242,7 +2242,7 @@
         <v>0.642</v>
       </c>
       <c r="J20" t="n">
-        <v>16.09</v>
+        <v>1.61</v>
       </c>
       <c r="K20" t="n">
         <v>79.92</v>
@@ -2331,7 +2331,7 @@
         <v>0.577</v>
       </c>
       <c r="J21" t="n">
-        <v>16.44</v>
+        <v>1.64</v>
       </c>
       <c r="K21" t="n">
         <v>75.92</v>
